--- a/data/elif_test1_2024-04-19_18h23.39.643.xlsx
+++ b/data/elif_test1_2024-04-19_18h23.39.643.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\CrestAwardProg\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6EAF496-4D84-4F8B-9E81-C552B49CD469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{4D9180C7-558E-4C13-9ECC-DE612448DDFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620"/>
   </bookViews>
